--- a/data/s0/Annelinn/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s0/Annelinn/archetypes/pop_archetypes_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Annelinn\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5CBC82-6CF2-4CCE-9576-61F795D5BC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F76BFC-0689-43D6-904F-A4C2E0C5279C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -169,27 +169,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -204,7 +187,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,81 +204,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -582,7 +498,7 @@
     <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="7.88671875" customWidth="1"/>
     <col min="13" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="11.109375" style="5" customWidth="1"/>
+    <col min="17" max="18" width="11.109375" customWidth="1"/>
     <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -594,83 +510,83 @@
     <col min="28" max="29" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -699,10 +615,10 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
@@ -717,22 +633,22 @@
       <c r="P2">
         <v>0</v>
       </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="8">
-        <v>0</v>
-      </c>
-      <c r="T2" s="8">
-        <v>0</v>
-      </c>
-      <c r="U2" s="8">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
@@ -767,10 +683,10 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
       <c r="I3">
@@ -779,41 +695,41 @@
       <c r="J3">
         <v>0.1</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>62.984000000000002</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>2.94</v>
       </c>
-      <c r="O3" s="2">
-        <v>2.6709999999999998</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="Q3" s="6">
+      <c r="O3">
+        <v>2.6360000000000001</v>
+      </c>
+      <c r="P3">
+        <v>0.128</v>
+      </c>
+      <c r="Q3">
         <v>9999</v>
       </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
-        <v>177.70699999999999</v>
-      </c>
-      <c r="V3" s="8">
-        <v>14.922000000000001</v>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>177.58600000000001</v>
+      </c>
+      <c r="V3">
+        <v>13.057</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -847,10 +763,10 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
       <c r="I4">
@@ -859,10 +775,10 @@
       <c r="J4">
         <v>0.1</v>
       </c>
-      <c r="K4" s="2">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="K4">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="L4">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
@@ -871,30 +787,30 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="P4" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q4" s="6">
+      <c r="O4">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="P4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="Q4">
         <v>9999</v>
       </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <f>O4*0.5</f>
-        <v>0.41949999999999998</v>
-      </c>
-      <c r="T4" s="9">
+        <v>0.41349999999999998</v>
+      </c>
+      <c r="T4">
         <f>P4*0.5</f>
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="U4" s="8">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8">
+        <v>1.95E-2</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
@@ -929,10 +845,10 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
       <c r="I5">
@@ -941,41 +857,41 @@
       <c r="J5">
         <v>0.1</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>53.112000000000002</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>3.9049999999999998</v>
       </c>
-      <c r="O5" s="2">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="Q5" s="6">
+      <c r="O5">
+        <v>2.2759999999999998</v>
+      </c>
+      <c r="P5">
+        <v>0.159</v>
+      </c>
+      <c r="Q5">
         <v>9999</v>
       </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8">
-        <v>0</v>
-      </c>
-      <c r="U5" s="8">
-        <v>146.732</v>
-      </c>
-      <c r="V5" s="8">
-        <v>20.474</v>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>153.46100000000001</v>
+      </c>
+      <c r="V5">
+        <v>21.074999999999999</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1009,10 +925,10 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6">
@@ -1021,41 +937,41 @@
       <c r="J6">
         <v>0.1</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>0.05</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>43.322000000000003</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>2.206</v>
       </c>
-      <c r="O6" s="2">
-        <v>1.9750000000000001</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="O6">
+        <v>2.089</v>
+      </c>
+      <c r="P6">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="Q6">
         <v>9999</v>
       </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
-        <v>0</v>
-      </c>
-      <c r="U6" s="8">
-        <v>37.835000000000001</v>
-      </c>
-      <c r="V6" s="8">
-        <v>60.267000000000003</v>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>45.908999999999999</v>
+      </c>
+      <c r="V6">
+        <v>61.256</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1089,10 +1005,10 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="I7">
@@ -1101,47 +1017,48 @@
       <c r="J7">
         <v>0.1</v>
       </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7">
+        <f>2/17</f>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="L7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7">
         <f>293.323/30</f>
         <v>9.7774333333333328</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7">
         <f>38.284/30</f>
         <v>1.2761333333333333</v>
       </c>
-      <c r="O7" s="7">
-        <f>12.372/30</f>
-        <v>0.41239999999999999</v>
-      </c>
-      <c r="P7" s="7">
-        <f>1.668/30</f>
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="Q7" s="6">
+      <c r="O7" s="1">
+        <f>13.877/45</f>
+        <v>0.30837777777777781</v>
+      </c>
+      <c r="P7" s="1">
+        <f>1.793/45</f>
+        <v>3.9844444444444446E-2</v>
+      </c>
+      <c r="Q7">
         <v>9999</v>
       </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <f>740.509/30</f>
-        <v>24.683633333333333</v>
-      </c>
-      <c r="V7" s="8">
-        <f>271.113/30</f>
-        <v>9.0371000000000006</v>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <f>836.791/45</f>
+        <v>18.595355555555557</v>
+      </c>
+      <c r="V7" s="1">
+        <f>296.405/45</f>
+        <v>6.586777777777777</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1175,10 +1092,10 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>37</v>
       </c>
       <c r="I8">
@@ -1187,10 +1104,11 @@
       <c r="J8">
         <v>0.1</v>
       </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="K8">
+        <f>2/17</f>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="L8">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
@@ -1199,32 +1117,32 @@
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8" s="2">
-        <f>5.542/30</f>
-        <v>0.18473333333333333</v>
-      </c>
-      <c r="P8" s="2">
-        <f>1.704/30</f>
-        <v>5.6799999999999996E-2</v>
-      </c>
-      <c r="Q8" s="6">
+      <c r="O8" s="1">
+        <f>5.657/45</f>
+        <v>0.12571111111111111</v>
+      </c>
+      <c r="P8" s="1">
+        <f>1.622/45</f>
+        <v>3.6044444444444448E-2</v>
+      </c>
+      <c r="Q8">
         <v>9999</v>
       </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <f>O8*0.5</f>
-        <v>9.2366666666666666E-2</v>
-      </c>
-      <c r="T8" s="9">
+        <v>6.2855555555555553E-2</v>
+      </c>
+      <c r="T8">
         <f>P8*0.5</f>
-        <v>2.8399999999999998E-2</v>
-      </c>
-      <c r="U8" s="8">
-        <v>0</v>
-      </c>
-      <c r="V8" s="8">
+        <v>1.8022222222222224E-2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
         <v>0</v>
       </c>
       <c r="W8">
@@ -1259,10 +1177,10 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
       <c r="I9">
@@ -1271,47 +1189,44 @@
       <c r="J9">
         <v>0.1</v>
       </c>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="K9">
+        <f>2/17</f>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="L9">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <f>357.554/30</f>
         <v>11.918466666666665</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <f>68.396/30</f>
         <v>2.2798666666666665</v>
       </c>
-      <c r="O9" s="7">
-        <f>16.118/30</f>
-        <v>0.53726666666666667</v>
-      </c>
-      <c r="P9" s="7">
-        <f>2.637/30</f>
-        <v>8.7900000000000006E-2</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="O9">
+        <v>16.956</v>
+      </c>
+      <c r="P9">
+        <v>2.524</v>
+      </c>
+      <c r="Q9">
         <v>9999</v>
       </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8">
-        <f>411.627/30</f>
-        <v>13.7209</v>
-      </c>
-      <c r="V9" s="8">
-        <f>386.868/30</f>
-        <v>12.8956</v>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>472.11500000000001</v>
+      </c>
+      <c r="V9">
+        <v>376.47300000000001</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1345,10 +1260,10 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" t="s">
         <v>37</v>
       </c>
       <c r="I10">
@@ -1357,10 +1272,10 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10" s="2">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="L10">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M10">
@@ -1369,30 +1284,30 @@
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10" s="2">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="P10" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q10" s="6">
+      <c r="O10">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="P10">
+        <v>3.9E-2</v>
+      </c>
+      <c r="Q10">
         <v>9999</v>
       </c>
-      <c r="R10" s="5">
-        <v>0</v>
-      </c>
-      <c r="S10" s="9">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <f>O10*0.5</f>
-        <v>0.41949999999999998</v>
-      </c>
-      <c r="T10" s="9">
+        <v>0.41349999999999998</v>
+      </c>
+      <c r="T10">
         <f>P10*0.5</f>
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="U10" s="8">
-        <v>0</v>
-      </c>
-      <c r="V10" s="8">
+        <v>1.95E-2</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
@@ -1409,56 +1324,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:J10">
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A11:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="23" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4:P4">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:P8">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M10:P10">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:XFD3">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:R10">
-    <cfRule type="cellIs" dxfId="3" priority="20" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S7">
-    <cfRule type="cellIs" dxfId="2" priority="16" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S8:T9">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:XFD9 S10:XFD10">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/s0/Annelinn/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s0/Annelinn/archetypes/pop_archetypes_transport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Annelinn\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F76BFC-0689-43D6-904F-A4C2E0C5279C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08897BC1-7760-4889-B201-244BE9176FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -188,6 +188,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -204,9 +210,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -1272,8 +1280,8 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10">
-        <v>6.6000000000000003E-2</v>
+      <c r="K10" s="2">
+        <v>0.39903264812575578</v>
       </c>
       <c r="L10">
         <v>1.0000000000000001E-5</v>
@@ -1322,6 +1330,18 @@
       <c r="Z10">
         <v>100</v>
       </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
